--- a/artfynd/A 52741-2022 artfynd.xlsx
+++ b/artfynd/A 52741-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>53489279</v>
       </c>
       <c r="B3" t="n">
-        <v>58656</v>
+        <v>58711</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52741-2022 artfynd.xlsx
+++ b/artfynd/A 52741-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>53489279</v>
       </c>
       <c r="B3" t="n">
-        <v>58711</v>
+        <v>58724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52741-2022 artfynd.xlsx
+++ b/artfynd/A 52741-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>53489279</v>
       </c>
       <c r="B3" t="n">
-        <v>58724</v>
+        <v>58726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52741-2022 artfynd.xlsx
+++ b/artfynd/A 52741-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>53489279</v>
       </c>
       <c r="B3" t="n">
-        <v>58726</v>
+        <v>58736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52741-2022 artfynd.xlsx
+++ b/artfynd/A 52741-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>53489279</v>
       </c>
       <c r="B3" t="n">
-        <v>58736</v>
+        <v>58738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52741-2022 artfynd.xlsx
+++ b/artfynd/A 52741-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>53489279</v>
       </c>
       <c r="B3" t="n">
-        <v>58738</v>
+        <v>58740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52741-2022 artfynd.xlsx
+++ b/artfynd/A 52741-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>53489279</v>
       </c>
       <c r="B3" t="n">
-        <v>58740</v>
+        <v>58743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
